--- a/TPM_data.xlsx
+++ b/TPM_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YebelayBerehan\Desktop\Claude_Projects\Claude files\Plots\tpm_review_quarto_2026-07-10\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mzeef.sharepoint.com/sites/P25117/Freigegebene Dokumente/Working Files/06_Workshops_Presentations/Annual TPM Performance Review 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E78C73C-0A14-482D-A427-424FF45E519C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="14_{668C71A4-3DC1-4FE5-B23D-14C256F0E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37F3B984-5727-4134-AD4E-5303344BB5D9}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="7" xr2:uid="{3916B5A7-B48A-4807-822B-1E2B02DB7B94}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="19366" windowHeight="20963" firstSheet="5" activeTab="11" xr2:uid="{3916B5A7-B48A-4807-822B-1E2B02DB7B94}"/>
   </bookViews>
   <sheets>
     <sheet name="monitoring_plans" sheetId="12" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <sheet name="budget" sheetId="8" r:id="rId11"/>
     <sheet name="finance" sheetId="9" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="100">
   <si>
     <t>Month</t>
   </si>
@@ -394,18 +394,12 @@
       <name val="Aptos Narrow"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -465,7 +459,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -496,7 +490,6 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -507,64 +500,69 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -900,9 +898,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01CF1E1D-002A-4AFB-AC0C-9BD258560A22}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -919,7 +917,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
         <v>45901</v>
       </c>
@@ -933,7 +931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
         <v>45931</v>
       </c>
@@ -947,7 +945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="7">
         <v>45962</v>
       </c>
@@ -961,7 +959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="7">
         <v>45992</v>
       </c>
@@ -978,7 +976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="7">
         <v>46023</v>
       </c>
@@ -995,7 +993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="7">
         <v>46054</v>
       </c>
@@ -1012,7 +1010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="7">
         <v>46082</v>
       </c>
@@ -1029,7 +1027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="7">
         <v>46113</v>
       </c>
@@ -1046,7 +1044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="7">
         <v>46143</v>
       </c>
@@ -1063,7 +1061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="7">
         <v>46174</v>
       </c>
@@ -1088,12 +1086,12 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEEB1F48-752F-49BE-BA42-AA8856804B57}">
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="5" max="5" width="8.44140625" customWidth="1"/>
+    <col min="5" max="5" width="8.46484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1113,7 +1111,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
         <v>45870</v>
       </c>
@@ -1121,27 +1119,27 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
         <v>45901</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="7">
         <v>45931</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="7">
         <v>45962</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="7">
         <v>45992</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="7">
         <v>46023</v>
       </c>
@@ -1152,7 +1150,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="7">
         <v>46054</v>
       </c>
@@ -1160,12 +1158,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="7">
         <v>46082</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="7">
         <v>46113</v>
       </c>
@@ -1173,7 +1171,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="7">
         <v>46143</v>
       </c>
@@ -1181,15 +1179,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="7">
         <v>46174</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="7"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" s="7"/>
     </row>
   </sheetData>
@@ -1200,25 +1198,25 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{433A999F-8C75-4E97-A87F-40321E159D51}">
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="7" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="6" width="10.109375" customWidth="1"/>
-    <col min="7" max="8" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.86328125" customWidth="1"/>
+    <col min="3" max="6" width="10.1328125" customWidth="1"/>
+    <col min="7" max="8" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.46484375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.86328125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.88671875" customWidth="1"/>
+    <col min="13" max="14" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.46484375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.86328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.53125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.86328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
         <v>74</v>
       </c>
@@ -1277,7 +1275,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1340,7 +1338,7 @@
         <v>7200</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1404,7 +1402,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1467,7 +1465,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1530,7 +1528,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -1593,7 +1591,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -1656,7 +1654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -1719,7 +1717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>2</v>
       </c>
@@ -1782,7 +1780,7 @@
         <v>3933.3333333333335</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -1845,7 +1843,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -1908,7 +1906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -1971,7 +1969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -2034,7 +2032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
         <v>3</v>
       </c>
@@ -2105,14 +2103,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{820D0EDE-F07A-4579-B773-F319C167E0A2}">
   <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="12.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="6" max="6" width="12.796875" customWidth="1"/>
+    <col min="7" max="7" width="13.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2135,13 +2133,13 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
         <v>45870</v>
       </c>
       <c r="B2" s="3">
-        <f>2/3*(9526+34140+337.5)</f>
-        <v>29335.666666666664</v>
+        <f>2/3*(9526+34140+337.5)+22200</f>
+        <v>51535.666666666664</v>
       </c>
       <c r="C2" s="3">
         <v>29033.93</v>
@@ -2152,7 +2150,7 @@
       </c>
       <c r="E2" s="3">
         <f t="shared" ref="E2:E14" si="1">B2-D2</f>
-        <v>301.73666666666395</v>
+        <v>22501.736666666664</v>
       </c>
       <c r="F2" s="3">
         <f>C2*1.15</f>
@@ -2163,13 +2161,13 @@
         <v>33389.019499999995</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
         <v>45901</v>
       </c>
       <c r="B3" s="3">
-        <f>22200+10650+9526+34140+337.5</f>
-        <v>76853.5</v>
+        <f>10650+9526+34140+337.5</f>
+        <v>54653.5</v>
       </c>
       <c r="C3" s="3">
         <v>54018</v>
@@ -2180,7 +2178,7 @@
       </c>
       <c r="E3" s="3">
         <f t="shared" si="1"/>
-        <v>22835.5</v>
+        <v>635.5</v>
       </c>
       <c r="F3" s="3">
         <f t="shared" ref="F3:G14" si="2">C3*1.15</f>
@@ -2191,7 +2189,7 @@
         <v>62120.7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="7">
         <v>45931</v>
       </c>
@@ -2219,7 +2217,7 @@
         <v>63064.401499999993</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="7">
         <v>45962</v>
       </c>
@@ -2247,7 +2245,7 @@
         <v>48466.52</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" s="7">
         <v>45992</v>
       </c>
@@ -2275,7 +2273,7 @@
         <v>49325.799999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" s="7">
         <v>46023</v>
       </c>
@@ -2303,7 +2301,7 @@
         <v>55397.799999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" s="7">
         <v>46054</v>
       </c>
@@ -2331,7 +2329,7 @@
         <v>49512.1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" s="7">
         <v>46082</v>
       </c>
@@ -2359,7 +2357,7 @@
         <v>49953.7</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="7">
         <v>46113</v>
       </c>
@@ -2387,7 +2385,7 @@
         <v>69273.7</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" s="7">
         <v>46143</v>
       </c>
@@ -2415,7 +2413,7 @@
         <v>61075.591499999995</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" s="7">
         <v>46174</v>
       </c>
@@ -2437,7 +2435,7 @@
         <v>49946.799999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" s="7">
         <v>46204</v>
       </c>
@@ -2459,7 +2457,7 @@
         <v>49946.799999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" s="7">
         <v>46235</v>
       </c>
@@ -2482,46 +2480,46 @@
         <v>16648.933333333334</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" s="8"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" s="8"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A17" s="8"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A18" s="8"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A19" s="8"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A20" s="8"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A21" s="8"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A22" s="8"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A23" s="8"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A24" s="8"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A25" s="8"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A26" s="8"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A27" s="8"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A28" s="8"/>
     </row>
   </sheetData>
@@ -2532,12 +2530,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3987CE4A-FD41-4438-B1B1-1043AEF3C11E}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="4" max="4" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2551,12 +2549,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
         <v>45870</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
         <v>45901</v>
       </c>
@@ -2564,7 +2562,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="7">
         <v>45931</v>
       </c>
@@ -2578,7 +2576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="7">
         <v>45962</v>
       </c>
@@ -2589,7 +2587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="7">
         <v>45992</v>
       </c>
@@ -2600,7 +2598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="7">
         <v>46023</v>
       </c>
@@ -2611,7 +2609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="7">
         <v>46054</v>
       </c>
@@ -2625,7 +2623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="7">
         <v>46082</v>
       </c>
@@ -2636,7 +2634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="7">
         <v>46113</v>
       </c>
@@ -2647,7 +2645,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" s="7">
         <v>46143</v>
       </c>
@@ -2658,7 +2656,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" s="7">
         <v>46174</v>
       </c>
@@ -2669,7 +2667,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" s="10">
         <v>46204</v>
       </c>
@@ -2684,116 +2682,150 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{834758E2-6474-4743-9186-B31DDC8C65DD}">
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="4" width="11.44140625" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" customWidth="1"/>
+    <col min="3" max="5" width="11.46484375" customWidth="1"/>
+    <col min="6" max="6" width="9.86328125" customWidth="1"/>
+    <col min="7" max="7" width="10.46484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
         <v>45870</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B2" s="7"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
         <v>45901</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B3" s="30">
+        <v>31</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="7">
         <v>45931</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4" s="30">
+        <v>14</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="7">
         <v>45962</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="30">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" s="7">
         <v>45992</v>
       </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="30">
+        <v>22</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" s="7">
         <v>46023</v>
       </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="30">
+        <v>25</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" s="7">
         <v>46054</v>
       </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="30">
+        <v>27</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" s="7">
         <v>46082</v>
       </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="30">
+        <v>6</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="7">
         <v>46113</v>
       </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="30">
+        <v>10</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" s="7">
         <v>46143</v>
       </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="30">
+        <v>11</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" s="7">
         <v>46174</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="30">
+        <v>3</v>
+      </c>
+      <c r="C12">
         <v>1</v>
       </c>
     </row>
@@ -2804,16 +2836,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F8E7062-3546-44DB-9B91-9E94676B958C}">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="7.21875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.21875" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.19921875" style="1" customWidth="1"/>
+    <col min="2" max="3" width="9.19921875" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" customWidth="1"/>
+    <col min="5" max="5" width="15.46484375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
         <v>9</v>
       </c>
@@ -2821,24 +2853,31 @@
         <v>50</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="9">
         <v>4</v>
       </c>
       <c r="B2">
         <v>3</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C2">
+        <f>31+28+31</f>
+        <v>90</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="9">
         <v>1</v>
       </c>
@@ -2846,16 +2885,19 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="9"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="9"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="9"/>
     </row>
   </sheetData>
@@ -2866,453 +2908,453 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE6C9A8F-1670-4E3F-AD65-057736711737}">
   <dimension ref="A1:N12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="9" width="9.44140625" customWidth="1"/>
-    <col min="10" max="11" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="9" width="9.46484375" customWidth="1"/>
+    <col min="10" max="11" width="9.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="35" t="s">
+    <row r="1" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="34" t="s">
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="16" t="s">
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="33" t="s">
+      <c r="L1" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-    </row>
-    <row r="2" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="12"/>
-      <c r="B2" s="17" t="s">
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+    </row>
+    <row r="2" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="11"/>
+      <c r="B2" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="K2" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="L2" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="M2" s="20" t="s">
+      <c r="M2" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="N2" s="20" t="s">
+      <c r="N2" s="19" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="12">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A3" s="26">
         <v>45901</v>
       </c>
-      <c r="B3" s="17">
+      <c r="B3" s="16">
         <v>175</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="18">
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="17">
         <v>192</v>
       </c>
-      <c r="I3" s="18">
-        <v>0</v>
-      </c>
-      <c r="J3" s="18">
-        <v>0</v>
-      </c>
-      <c r="K3" s="19">
+      <c r="I3" s="17">
+        <v>0</v>
+      </c>
+      <c r="J3" s="17">
+        <v>0</v>
+      </c>
+      <c r="K3" s="18">
         <v>126</v>
       </c>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="20"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="12">
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A4" s="26">
         <v>45931</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="16">
         <v>148</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="16">
         <v>2</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="16">
         <v>2</v>
       </c>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="18">
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="17">
         <v>142</v>
       </c>
-      <c r="I4" s="18">
+      <c r="I4" s="17">
         <v>12</v>
       </c>
-      <c r="J4" s="18">
-        <v>0</v>
-      </c>
-      <c r="K4" s="19">
+      <c r="J4" s="17">
+        <v>0</v>
+      </c>
+      <c r="K4" s="18">
         <v>149</v>
       </c>
-      <c r="L4" s="20"/>
-      <c r="M4" s="20"/>
-      <c r="N4" s="20"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="12">
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A5" s="26">
         <v>45962</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="16">
         <v>155</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="16">
         <v>2</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="16">
         <v>2</v>
       </c>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17">
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16">
         <v>9</v>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="17">
         <v>266</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="17">
         <v>19</v>
       </c>
-      <c r="J5" s="18">
+      <c r="J5" s="17">
         <v>9</v>
       </c>
-      <c r="K5" s="19">
+      <c r="K5" s="18">
         <v>285</v>
       </c>
-      <c r="L5" s="20"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="20"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="12">
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A6" s="26">
         <v>45992</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="16">
         <v>35</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="16">
         <v>2</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="16">
         <v>2</v>
       </c>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17">
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16">
         <v>9</v>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="17">
         <v>122</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="17">
         <v>18</v>
       </c>
-      <c r="J6" s="18">
+      <c r="J6" s="17">
         <v>7</v>
       </c>
-      <c r="K6" s="19">
+      <c r="K6" s="18">
         <v>263</v>
       </c>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
-      <c r="N6" s="20"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="12">
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A7" s="26">
         <v>46023</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="16">
         <v>101</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="16">
         <v>2</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="16">
         <v>2</v>
       </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="18">
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="17">
         <v>155</v>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="17">
         <v>6</v>
       </c>
-      <c r="J7" s="18">
-        <v>0</v>
-      </c>
-      <c r="K7" s="19"/>
-      <c r="L7" s="20">
+      <c r="J7" s="17">
+        <v>0</v>
+      </c>
+      <c r="K7" s="18"/>
+      <c r="L7" s="19">
         <v>186</v>
       </c>
-      <c r="M7" s="20"/>
-      <c r="N7" s="20">
+      <c r="M7" s="19"/>
+      <c r="N7" s="19">
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="12">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A8" s="26">
         <v>46054</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="16">
         <v>97</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="16">
         <v>2</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="16">
         <v>2</v>
       </c>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17">
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16">
         <v>2</v>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="17">
         <v>309</v>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="17">
         <v>12</v>
       </c>
-      <c r="J8" s="18">
+      <c r="J8" s="17">
         <v>4</v>
       </c>
-      <c r="K8" s="19">
+      <c r="K8" s="18">
         <v>237</v>
       </c>
-      <c r="L8" s="20">
+      <c r="L8" s="19">
         <v>132</v>
       </c>
-      <c r="M8" s="20">
+      <c r="M8" s="19">
         <v>28</v>
       </c>
-      <c r="N8" s="20">
+      <c r="N8" s="19">
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="12">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A9" s="26">
         <v>46082</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="16">
         <v>200</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="16">
         <v>2</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="16">
         <v>2</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="16">
         <v>16</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="16">
         <v>5</v>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="16">
         <v>16</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="17">
         <v>323</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="17">
         <v>15</v>
       </c>
-      <c r="J9" s="18">
+      <c r="J9" s="17">
         <v>10</v>
       </c>
-      <c r="K9" s="19">
+      <c r="K9" s="18">
         <v>277</v>
       </c>
-      <c r="L9" s="20">
+      <c r="L9" s="19">
         <v>198</v>
       </c>
-      <c r="M9" s="20">
+      <c r="M9" s="19">
         <v>76</v>
       </c>
-      <c r="N9" s="20">
+      <c r="N9" s="19">
         <v>67</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="12">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A10" s="26">
         <v>46113</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="16">
         <v>185</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="16">
         <v>2</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="16">
         <v>2</v>
       </c>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17">
+      <c r="E10" s="16"/>
+      <c r="F10" s="16">
         <v>5</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="16">
         <v>13</v>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="17">
         <v>156</v>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="17">
         <v>11</v>
       </c>
-      <c r="J10" s="18">
+      <c r="J10" s="17">
         <v>2</v>
       </c>
-      <c r="K10" s="19">
+      <c r="K10" s="18">
         <v>229</v>
       </c>
-      <c r="L10" s="20">
+      <c r="L10" s="19">
         <v>113</v>
       </c>
-      <c r="M10" s="20">
+      <c r="M10" s="19">
         <v>54</v>
       </c>
-      <c r="N10" s="20">
+      <c r="N10" s="19">
         <v>133</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="12">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A11" s="26">
         <v>46143</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="16">
         <v>188</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="16">
         <v>2</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="16">
         <v>2</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="16">
         <v>11</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="16">
         <v>5</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="16">
         <v>13</v>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="17">
         <v>132</v>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="17">
         <v>25</v>
       </c>
-      <c r="J11" s="18">
+      <c r="J11" s="17">
         <v>9</v>
       </c>
-      <c r="K11" s="19">
+      <c r="K11" s="18">
         <v>184</v>
       </c>
-      <c r="L11" s="20">
+      <c r="L11" s="19">
         <v>301</v>
       </c>
-      <c r="M11" s="20">
+      <c r="M11" s="19">
         <v>63</v>
       </c>
-      <c r="N11" s="20">
+      <c r="N11" s="19">
         <v>122</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="12">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A12" s="26">
         <v>46174</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="16">
         <v>169</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="16">
         <v>2</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="16">
         <v>2</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="16">
         <v>9</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="16">
         <v>5</v>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="16">
         <v>6</v>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="17">
         <v>145</v>
       </c>
-      <c r="I12" s="18">
+      <c r="I12" s="17">
         <v>59</v>
       </c>
-      <c r="J12" s="18">
+      <c r="J12" s="17">
         <v>5</v>
       </c>
-      <c r="K12" s="19">
+      <c r="K12" s="18">
         <v>41</v>
       </c>
-      <c r="L12" s="20">
-        <v>1</v>
-      </c>
-      <c r="M12" s="20">
+      <c r="L12" s="19">
+        <v>1</v>
+      </c>
+      <c r="M12" s="19">
         <v>23</v>
       </c>
-      <c r="N12" s="20">
+      <c r="N12" s="19">
         <v>96</v>
       </c>
     </row>
@@ -3329,339 +3371,343 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A655B969-0322-46FB-BBE7-98548BAE1234}">
   <dimension ref="A1:Q15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="4" max="5" width="8.86328125"/>
+    <col min="13" max="16" width="8.86328125"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="31" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="32" t="s">
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="23" t="s">
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="22" t="s">
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="21" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="14"/>
-      <c r="B2" s="24" t="s">
+    <row r="2" spans="1:17" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A2" s="13"/>
+      <c r="B2" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D2" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="F2" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="G2" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="H2" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="I2" s="25" t="s">
+      <c r="I2" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="J2" s="26" t="s">
+      <c r="J2" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="L2" s="26" t="s">
+      <c r="L2" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="M2" s="26" t="s">
+      <c r="M2" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="N2" s="26" t="s">
+      <c r="N2" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="O2" s="26" t="s">
+      <c r="O2" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="P2" s="26" t="s">
+      <c r="P2" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="Q2" s="14" t="s">
+      <c r="Q2" s="13" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="27">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A3" s="26">
         <v>46290</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
-      <c r="Q3" s="14"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="27">
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="13"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A4" s="26">
         <v>46320</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="14"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="27">
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="25"/>
+      <c r="O4" s="25"/>
+      <c r="P4" s="25"/>
+      <c r="Q4" s="13"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A5" s="26">
         <v>46351</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="26"/>
-      <c r="Q5" s="14"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="27">
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="25"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="25"/>
+      <c r="Q5" s="13"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A6" s="26">
         <v>46381</v>
       </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24">
+      <c r="B6" s="23"/>
+      <c r="C6" s="23">
         <v>6</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="23">
         <v>12</v>
       </c>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="25">
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="24">
         <v>10</v>
       </c>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="26"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="26"/>
-      <c r="P6" s="26"/>
-      <c r="Q6" s="14">
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="25"/>
+      <c r="P6" s="25"/>
+      <c r="Q6" s="13">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="27">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A7" s="26">
         <v>46048</v>
       </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24">
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23">
         <v>3</v>
       </c>
-      <c r="F7" s="24"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25">
+      <c r="F7" s="23"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24">
         <v>11</v>
       </c>
-      <c r="J7" s="26">
+      <c r="J7" s="25">
         <v>11</v>
       </c>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
-      <c r="P7" s="26"/>
-      <c r="Q7" s="14"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="27">
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="25"/>
+      <c r="Q7" s="13"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A8" s="26">
         <v>46079</v>
       </c>
-      <c r="B8" s="24"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24">
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23">
         <v>3</v>
       </c>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="14"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="27">
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="13"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A9" s="26">
         <v>46107</v>
       </c>
-      <c r="B9" s="24"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="26"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="26">
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="25">
         <v>8</v>
       </c>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="14"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="27">
+      <c r="P9" s="25"/>
+      <c r="Q9" s="13"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A10" s="26">
         <v>46138</v>
       </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="26"/>
-      <c r="Q10" s="14"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="27">
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="25"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="25"/>
+      <c r="Q10" s="13"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A11" s="26">
         <v>46168</v>
       </c>
-      <c r="B11" s="24"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="26"/>
-      <c r="M11" s="26"/>
-      <c r="N11" s="26"/>
-      <c r="O11" s="26"/>
-      <c r="P11" s="26"/>
-      <c r="Q11" s="14"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="27">
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="25"/>
+      <c r="P11" s="25"/>
+      <c r="Q11" s="13"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A12" s="26">
         <v>46199</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="23">
         <v>16</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="29">
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="28">
         <v>13</v>
       </c>
-      <c r="H12" s="29">
+      <c r="H12" s="28">
         <v>11</v>
       </c>
-      <c r="I12" s="29"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="30">
+      <c r="I12" s="28"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="29">
         <v>15</v>
       </c>
-      <c r="L12" s="30">
+      <c r="L12" s="29">
         <v>11</v>
       </c>
-      <c r="M12" s="30">
+      <c r="M12" s="29">
         <v>8</v>
       </c>
-      <c r="N12" s="30">
+      <c r="N12" s="29">
         <v>11</v>
       </c>
-      <c r="O12" s="30"/>
-      <c r="P12" s="30">
+      <c r="O12" s="29"/>
+      <c r="P12" s="29">
         <v>8</v>
       </c>
-      <c r="Q12" s="15">
+      <c r="Q12" s="14">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="J15" s="21" t="s">
+    <row r="15" spans="1:17" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="J15" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="K15" s="21"/>
+      <c r="K15" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3675,12 +3721,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3459EC2F-9022-4F3C-8F04-9817AC5B6AAB}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="13.77734375" customWidth="1"/>
+    <col min="2" max="2" width="13.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -3697,7 +3743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="7">
         <v>45870</v>
       </c>
@@ -3715,7 +3761,7 @@
         <v>0.60000000000000009</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="7">
         <v>45901</v>
       </c>
@@ -3733,7 +3779,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="7">
         <v>45931</v>
       </c>
@@ -3751,7 +3797,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="7">
         <v>45962</v>
       </c>
@@ -3769,7 +3815,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="7">
         <v>45992</v>
       </c>
@@ -3787,7 +3833,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="7">
         <v>46023</v>
       </c>
@@ -3805,7 +3851,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="7">
         <v>46054</v>
       </c>
@@ -3823,7 +3869,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="7">
         <v>46082</v>
       </c>
@@ -3841,7 +3887,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="7">
         <v>46113</v>
       </c>
@@ -3859,7 +3905,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="7">
         <v>46143</v>
       </c>
@@ -3877,7 +3923,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="7">
         <v>46174</v>
       </c>
@@ -3903,15 +3949,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ED9E1C1-C174-4817-8C8A-9919290A9E4C}">
   <dimension ref="A1:E18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" customWidth="1"/>
-    <col min="5" max="5" width="13.77734375" customWidth="1"/>
+    <col min="1" max="1" width="8.796875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1328125" customWidth="1"/>
+    <col min="4" max="4" width="7.53125" customWidth="1"/>
+    <col min="5" max="5" width="13.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
         <v>57</v>
       </c>
@@ -3928,12 +3974,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B2" s="7">
         <v>45870</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3950,7 +3996,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -3967,7 +4013,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -3977,14 +4023,14 @@
       <c r="C5" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="36">
         <v>4</v>
       </c>
       <c r="E5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -4001,22 +4047,22 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B7" s="7">
         <v>45962</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B8" s="7">
         <v>45992</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B9" s="7">
         <v>46023</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>3</v>
       </c>
@@ -4033,7 +4079,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <v>3</v>
       </c>
@@ -4043,24 +4089,24 @@
       <c r="C11" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="36">
         <v>1</v>
       </c>
       <c r="E11" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B12" s="7">
         <v>46082</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B13" s="10">
         <v>46113</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
         <v>4</v>
       </c>
@@ -4077,7 +4123,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
         <v>4</v>
       </c>
@@ -4094,7 +4140,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
         <v>4</v>
       </c>
@@ -4111,7 +4157,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
         <v>4</v>
       </c>
@@ -4121,14 +4167,11 @@
       <c r="C17" t="s">
         <v>37</v>
       </c>
-      <c r="D17">
-        <v>3</v>
-      </c>
       <c r="E17" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B18" s="10">
         <v>46174</v>
       </c>
@@ -4141,15 +4184,15 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BC2309D-0DCA-4AFF-99AF-FE18AE8086CF}">
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.21875" customWidth="1"/>
-    <col min="4" max="4" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.46484375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.19921875" customWidth="1"/>
+    <col min="4" max="4" width="10.86328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
         <v>35</v>
       </c>
@@ -4166,7 +4209,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -4183,7 +4226,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -4200,7 +4243,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -4217,7 +4260,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -4234,7 +4277,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -4251,7 +4294,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -4268,7 +4311,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -4285,7 +4328,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -4302,7 +4345,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>5</v>
       </c>
@@ -4319,7 +4362,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <v>6</v>
       </c>
@@ -4336,7 +4379,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
         <v>7</v>
       </c>
@@ -4353,7 +4396,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
         <v>8</v>
       </c>
@@ -4370,7 +4413,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
         <v>8</v>
       </c>
@@ -4387,7 +4430,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
         <v>9</v>
       </c>
@@ -4404,7 +4447,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
         <v>9</v>
       </c>
@@ -4421,7 +4464,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
         <v>10</v>
       </c>
@@ -4438,7 +4481,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="1">
         <v>11</v>
       </c>
@@ -4455,7 +4498,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="1">
         <v>11</v>
       </c>
@@ -4472,7 +4515,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="1">
         <v>12</v>
       </c>
@@ -4489,7 +4532,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1">
         <v>12</v>
       </c>
@@ -4506,7 +4549,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="1">
         <v>13</v>
       </c>
@@ -4529,17 +4572,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f1b5c029-f99d-4007-83c8-e86a87dae2c0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b1f2453e-b84f-40dd-ae62-17f8f59f3b8f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -4548,7 +4580,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100CC0EFE16C5685847AF53F415157196AB" ma:contentTypeVersion="10" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="25e3ba501f4236ce3f30ac36e0670a7a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f1b5c029-f99d-4007-83c8-e86a87dae2c0" xmlns:ns3="b1f2453e-b84f-40dd-ae62-17f8f59f3b8f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ba4304f73c53f4215cc939dedaa1b40a" ns2:_="" ns3:_="">
     <xsd:import namespace="f1b5c029-f99d-4007-83c8-e86a87dae2c0"/>
@@ -4737,20 +4769,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C62E9485-3457-417A-8943-5A677C1E8E9E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="f1b5c029-f99d-4007-83c8-e86a87dae2c0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b1f2453e-b84f-40dd-ae62-17f8f59f3b8f"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f1b5c029-f99d-4007-83c8-e86a87dae2c0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b1f2453e-b84f-40dd-ae62-17f8f59f3b8f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B540B65-F983-4511-BF8B-36F63E533EA9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -4758,7 +4788,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F09DB090-3220-4E47-A6EC-E65A913BD319}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4776,4 +4806,17 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C62E9485-3457-417A-8943-5A677C1E8E9E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="f1b5c029-f99d-4007-83c8-e86a87dae2c0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b1f2453e-b84f-40dd-ae62-17f8f59f3b8f"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/TPM_data.xlsx
+++ b/TPM_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mzeef.sharepoint.com/sites/P25117/Freigegebene Dokumente/Working Files/06_Workshops_Presentations/Annual TPM Performance Review 2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YebelayBerehan\Desktop\TPM Review\TPM-Reviews\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="14_{668C71A4-3DC1-4FE5-B23D-14C256F0E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37F3B984-5727-4134-AD4E-5303344BB5D9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11FA4ABD-0BBB-4D84-94CB-ABB17A537414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="19366" windowHeight="20963" firstSheet="5" activeTab="11" xr2:uid="{3916B5A7-B48A-4807-822B-1E2B02DB7B94}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="4" xr2:uid="{3916B5A7-B48A-4807-822B-1E2B02DB7B94}"/>
   </bookViews>
   <sheets>
     <sheet name="monitoring_plans" sheetId="12" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <sheet name="budget" sheetId="8" r:id="rId11"/>
     <sheet name="finance" sheetId="9" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="191028" iterate="1"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -562,7 +562,9 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -898,9 +900,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01CF1E1D-002A-4AFB-AC0C-9BD258560A22}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -917,7 +919,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>45901</v>
       </c>
@@ -931,7 +933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>45931</v>
       </c>
@@ -945,7 +947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>45962</v>
       </c>
@@ -959,7 +961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>45992</v>
       </c>
@@ -976,7 +978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>46023</v>
       </c>
@@ -993,7 +995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>46054</v>
       </c>
@@ -1010,7 +1012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>46082</v>
       </c>
@@ -1027,7 +1029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>46113</v>
       </c>
@@ -1044,7 +1046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>46143</v>
       </c>
@@ -1061,7 +1063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>46174</v>
       </c>
@@ -1086,12 +1088,12 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEEB1F48-752F-49BE-BA42-AA8856804B57}">
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="8.46484375" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1111,7 +1113,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>45870</v>
       </c>
@@ -1119,27 +1121,27 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>45901</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>45931</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>45962</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>45992</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>46023</v>
       </c>
@@ -1150,7 +1152,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>46054</v>
       </c>
@@ -1158,12 +1160,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>46082</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>46113</v>
       </c>
@@ -1171,7 +1173,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>46143</v>
       </c>
@@ -1179,15 +1181,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>46174</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="7"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="7"/>
     </row>
   </sheetData>
@@ -1198,25 +1200,25 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{433A999F-8C75-4E97-A87F-40321E159D51}">
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.86328125" customWidth="1"/>
-    <col min="3" max="6" width="10.1328125" customWidth="1"/>
-    <col min="7" max="8" width="11.796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.46484375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.88671875" customWidth="1"/>
+    <col min="3" max="6" width="10.109375" customWidth="1"/>
+    <col min="7" max="8" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="11.796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.46484375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.86328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.53125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.86328125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.86328125" customWidth="1"/>
+    <col min="13" max="14" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>74</v>
       </c>
@@ -1275,7 +1277,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1338,7 +1340,7 @@
         <v>7200</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1402,7 +1404,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -1465,7 +1467,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1528,7 +1530,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -1591,7 +1593,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -1654,7 +1656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -1717,7 +1719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>2</v>
       </c>
@@ -1780,7 +1782,7 @@
         <v>3933.3333333333335</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -1843,7 +1845,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -1906,7 +1908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -1969,7 +1971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -2032,7 +2034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>3</v>
       </c>
@@ -2103,14 +2105,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{820D0EDE-F07A-4579-B773-F319C167E0A2}">
   <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="12.796875" customWidth="1"/>
-    <col min="7" max="7" width="13.19921875" customWidth="1"/>
+    <col min="6" max="6" width="12.77734375" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2133,7 +2135,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>45870</v>
       </c>
@@ -2161,7 +2163,7 @@
         <v>33389.019499999995</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>45901</v>
       </c>
@@ -2189,7 +2191,7 @@
         <v>62120.7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>45931</v>
       </c>
@@ -2217,7 +2219,7 @@
         <v>63064.401499999993</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>45962</v>
       </c>
@@ -2245,7 +2247,7 @@
         <v>48466.52</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>45992</v>
       </c>
@@ -2273,7 +2275,7 @@
         <v>49325.799999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>46023</v>
       </c>
@@ -2301,7 +2303,7 @@
         <v>55397.799999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>46054</v>
       </c>
@@ -2329,7 +2331,7 @@
         <v>49512.1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>46082</v>
       </c>
@@ -2357,7 +2359,7 @@
         <v>49953.7</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>46113</v>
       </c>
@@ -2385,7 +2387,7 @@
         <v>69273.7</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>46143</v>
       </c>
@@ -2413,7 +2415,7 @@
         <v>61075.591499999995</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>46174</v>
       </c>
@@ -2435,7 +2437,7 @@
         <v>49946.799999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>46204</v>
       </c>
@@ -2457,7 +2459,7 @@
         <v>49946.799999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>46235</v>
       </c>
@@ -2480,46 +2482,46 @@
         <v>16648.933333333334</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="8"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="8"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="8"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="8"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="8"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="8"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="8"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="8"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="8"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="8"/>
     </row>
   </sheetData>
@@ -2530,12 +2532,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3987CE4A-FD41-4438-B1B1-1043AEF3C11E}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2549,12 +2551,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>45870</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>45901</v>
       </c>
@@ -2562,7 +2564,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>45931</v>
       </c>
@@ -2576,7 +2578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>45962</v>
       </c>
@@ -2587,7 +2589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>45992</v>
       </c>
@@ -2598,7 +2600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>46023</v>
       </c>
@@ -2609,7 +2611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>46054</v>
       </c>
@@ -2623,7 +2625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>46082</v>
       </c>
@@ -2634,7 +2636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>46113</v>
       </c>
@@ -2645,7 +2647,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>46143</v>
       </c>
@@ -2656,7 +2658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>46174</v>
       </c>
@@ -2667,7 +2669,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
         <v>46204</v>
       </c>
@@ -2683,14 +2685,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{834758E2-6474-4743-9186-B31DDC8C65DD}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="5" width="11.46484375" customWidth="1"/>
-    <col min="6" max="6" width="9.86328125" customWidth="1"/>
-    <col min="7" max="7" width="10.46484375" customWidth="1"/>
+    <col min="3" max="5" width="11.44140625" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" customWidth="1"/>
+    <col min="7" max="7" width="10.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2713,13 +2715,13 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>45870</v>
       </c>
       <c r="B2" s="7"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>45901</v>
       </c>
@@ -2730,7 +2732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>45931</v>
       </c>
@@ -2741,7 +2743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>45962</v>
       </c>
@@ -2752,7 +2754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>45992</v>
       </c>
@@ -2763,7 +2765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>46023</v>
       </c>
@@ -2774,7 +2776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>46054</v>
       </c>
@@ -2785,7 +2787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>46082</v>
       </c>
@@ -2796,7 +2798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>46113</v>
       </c>
@@ -2807,7 +2809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>46143</v>
       </c>
@@ -2818,7 +2820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>46174</v>
       </c>
@@ -2837,15 +2839,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F8E7062-3546-44DB-9B91-9E94676B958C}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.19921875" style="1" customWidth="1"/>
-    <col min="2" max="3" width="9.19921875" customWidth="1"/>
+    <col min="1" max="1" width="7.21875" style="1" customWidth="1"/>
+    <col min="2" max="3" width="9.21875" customWidth="1"/>
     <col min="4" max="4" width="15.33203125" customWidth="1"/>
-    <col min="5" max="5" width="15.46484375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>9</v>
       </c>
@@ -2862,7 +2864,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="9">
         <v>4</v>
       </c>
@@ -2877,7 +2879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
         <v>1</v>
       </c>
@@ -2891,13 +2893,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
     </row>
   </sheetData>
@@ -2907,14 +2909,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE6C9A8F-1670-4E3F-AD65-057736711737}">
-  <dimension ref="A1:N12"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:N13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="9" width="9.46484375" customWidth="1"/>
-    <col min="10" max="11" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="9" width="9.44140625" customWidth="1"/>
+    <col min="10" max="11" width="9.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -2940,7 +2942,7 @@
       <c r="M1" s="31"/>
       <c r="N1" s="31"/>
     </row>
-    <row r="2" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11"/>
       <c r="B2" s="16" t="s">
         <v>81</v>
@@ -2982,7 +2984,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="26">
         <v>45901</v>
       </c>
@@ -3010,7 +3012,7 @@
       <c r="M3" s="19"/>
       <c r="N3" s="19"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="26">
         <v>45931</v>
       </c>
@@ -3042,7 +3044,7 @@
       <c r="M4" s="19"/>
       <c r="N4" s="19"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="26">
         <v>45962</v>
       </c>
@@ -3076,7 +3078,7 @@
       <c r="M5" s="19"/>
       <c r="N5" s="19"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="26">
         <v>45992</v>
       </c>
@@ -3110,7 +3112,7 @@
       <c r="M6" s="19"/>
       <c r="N6" s="19"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="26">
         <v>46023</v>
       </c>
@@ -3144,7 +3146,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="26">
         <v>46054</v>
       </c>
@@ -3184,7 +3186,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="26">
         <v>46082</v>
       </c>
@@ -3228,7 +3230,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="26">
         <v>46113</v>
       </c>
@@ -3270,7 +3272,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="26">
         <v>46143</v>
       </c>
@@ -3314,7 +3316,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="26">
         <v>46174</v>
       </c>
@@ -3356,6 +3358,12 @@
       </c>
       <c r="N12" s="19">
         <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K13" s="36">
+        <f>SUM(K2:K12)</f>
+        <v>1791</v>
       </c>
     </row>
   </sheetData>
@@ -3371,13 +3379,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A655B969-0322-46FB-BBE7-98548BAE1234}">
   <dimension ref="A1:Q15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="4" max="5" width="8.86328125"/>
-    <col min="13" max="16" width="8.86328125"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -3406,7 +3410,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="13"/>
       <c r="B2" s="23" t="s">
         <v>94</v>
@@ -3457,7 +3461,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="26">
         <v>46290</v>
       </c>
@@ -3478,7 +3482,7 @@
       <c r="P3" s="25"/>
       <c r="Q3" s="13"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="26">
         <v>46320</v>
       </c>
@@ -3499,7 +3503,7 @@
       <c r="P4" s="25"/>
       <c r="Q4" s="13"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="26">
         <v>46351</v>
       </c>
@@ -3520,7 +3524,7 @@
       <c r="P5" s="25"/>
       <c r="Q5" s="13"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="26">
         <v>46381</v>
       </c>
@@ -3549,7 +3553,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="26">
         <v>46048</v>
       </c>
@@ -3576,7 +3580,7 @@
       <c r="P7" s="25"/>
       <c r="Q7" s="13"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="26">
         <v>46079</v>
       </c>
@@ -3599,7 +3603,7 @@
       <c r="P8" s="25"/>
       <c r="Q8" s="13"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="26">
         <v>46107</v>
       </c>
@@ -3622,7 +3626,7 @@
       <c r="P9" s="25"/>
       <c r="Q9" s="13"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="26">
         <v>46138</v>
       </c>
@@ -3643,7 +3647,7 @@
       <c r="P10" s="25"/>
       <c r="Q10" s="13"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="26">
         <v>46168</v>
       </c>
@@ -3664,7 +3668,7 @@
       <c r="P11" s="25"/>
       <c r="Q11" s="13"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="26">
         <v>46199</v>
       </c>
@@ -3703,7 +3707,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:17" ht="86.4" x14ac:dyDescent="0.3">
       <c r="J15" s="20" t="s">
         <v>99</v>
       </c>
@@ -3721,12 +3725,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3459EC2F-9022-4F3C-8F04-9817AC5B6AAB}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.796875" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -3743,7 +3747,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>45870</v>
       </c>
@@ -3761,7 +3765,7 @@
         <v>0.60000000000000009</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>45901</v>
       </c>
@@ -3779,7 +3783,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>45931</v>
       </c>
@@ -3797,7 +3801,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>45962</v>
       </c>
@@ -3815,7 +3819,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>45992</v>
       </c>
@@ -3833,7 +3837,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>46023</v>
       </c>
@@ -3851,7 +3855,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>46054</v>
       </c>
@@ -3869,7 +3873,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>46082</v>
       </c>
@@ -3887,7 +3891,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>46113</v>
       </c>
@@ -3905,7 +3909,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>46143</v>
       </c>
@@ -3923,7 +3927,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>46174</v>
       </c>
@@ -3949,15 +3953,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ED9E1C1-C174-4817-8C8A-9919290A9E4C}">
   <dimension ref="A1:E18"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.796875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1328125" customWidth="1"/>
-    <col min="4" max="4" width="7.53125" customWidth="1"/>
-    <col min="5" max="5" width="13.796875" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" customWidth="1"/>
+    <col min="4" max="4" width="7.5546875" customWidth="1"/>
+    <col min="5" max="5" width="13.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>57</v>
       </c>
@@ -3974,12 +3978,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B2" s="7">
         <v>45870</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3996,7 +4000,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -4013,7 +4017,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -4023,14 +4027,14 @@
       <c r="C5" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="36">
+      <c r="D5">
         <v>4</v>
       </c>
       <c r="E5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -4047,22 +4051,22 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B7" s="7">
         <v>45962</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B8" s="7">
         <v>45992</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B9" s="7">
         <v>46023</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>3</v>
       </c>
@@ -4079,7 +4083,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>3</v>
       </c>
@@ -4089,24 +4093,24 @@
       <c r="C11" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="36">
+      <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B12" s="7">
         <v>46082</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B13" s="10">
         <v>46113</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>4</v>
       </c>
@@ -4123,7 +4127,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>4</v>
       </c>
@@ -4140,7 +4144,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>4</v>
       </c>
@@ -4157,7 +4161,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>4</v>
       </c>
@@ -4167,11 +4171,14 @@
       <c r="C17" t="s">
         <v>37</v>
       </c>
+      <c r="D17">
+        <v>3</v>
+      </c>
       <c r="E17" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B18" s="10">
         <v>46174</v>
       </c>
@@ -4184,15 +4191,15 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BC2309D-0DCA-4AFF-99AF-FE18AE8086CF}">
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.46484375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.19921875" customWidth="1"/>
-    <col min="4" max="4" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.21875" customWidth="1"/>
+    <col min="4" max="4" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>35</v>
       </c>
@@ -4209,7 +4216,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -4226,7 +4233,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -4243,7 +4250,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -4260,7 +4267,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -4277,7 +4284,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -4294,7 +4301,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -4311,7 +4318,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -4328,7 +4335,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -4345,7 +4352,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>5</v>
       </c>
@@ -4362,7 +4369,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>6</v>
       </c>
@@ -4379,7 +4386,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>7</v>
       </c>
@@ -4396,7 +4403,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>8</v>
       </c>
@@ -4413,7 +4420,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>8</v>
       </c>
@@ -4430,7 +4437,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>9</v>
       </c>
@@ -4447,7 +4454,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>9</v>
       </c>
@@ -4464,7 +4471,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>10</v>
       </c>
@@ -4481,7 +4488,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>11</v>
       </c>
@@ -4498,7 +4505,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>11</v>
       </c>
@@ -4515,7 +4522,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>12</v>
       </c>
@@ -4532,7 +4539,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>12</v>
       </c>
@@ -4549,7 +4556,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>13</v>
       </c>
@@ -4572,12 +4579,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f1b5c029-f99d-4007-83c8-e86a87dae2c0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b1f2453e-b84f-40dd-ae62-17f8f59f3b8f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4770,20 +4779,23 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f1b5c029-f99d-4007-83c8-e86a87dae2c0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="b1f2453e-b84f-40dd-ae62-17f8f59f3b8f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B540B65-F983-4511-BF8B-36F63E533EA9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C62E9485-3457-417A-8943-5A677C1E8E9E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="f1b5c029-f99d-4007-83c8-e86a87dae2c0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b1f2453e-b84f-40dd-ae62-17f8f59f3b8f"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4809,14 +4821,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C62E9485-3457-417A-8943-5A677C1E8E9E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B540B65-F983-4511-BF8B-36F63E533EA9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
-    <ds:schemaRef ds:uri="f1b5c029-f99d-4007-83c8-e86a87dae2c0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b1f2453e-b84f-40dd-ae62-17f8f59f3b8f"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema-instance"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>